--- a/Final_Main_Affiliates.xlsx
+++ b/Final_Main_Affiliates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jackprosser/Library/Mobile Documents/com~apple~CloudDocs/University/ECVP 2026/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mtoscani@bournemouth.ac.uk/Dropbox/ecvp_2026_website_final_clone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B252EC-5CD5-F546-80E4-305AC8FE79A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC597FE-B323-634B-ACB6-2389CB18F33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38420" yWindow="600" windowWidth="25600" windowHeight="21000" xr2:uid="{706473AC-54EE-B349-A1DD-9D10B08BDBB9}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17400" xr2:uid="{706473AC-54EE-B349-A1DD-9D10B08BDBB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8750" uniqueCount="3499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8845" uniqueCount="3549">
   <si>
     <t>Submission Id</t>
   </si>
@@ -10535,13 +10535,163 @@
   </si>
   <si>
     <t xml:space="preserve">Shao-Min </t>
+  </si>
+  <si>
+    <t>Frederick  A.A.</t>
+  </si>
+  <si>
+    <t>Kingdom</t>
+  </si>
+  <si>
+    <t>Tomer</t>
+  </si>
+  <si>
+    <t>Bouhnik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marika </t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floortje </t>
+  </si>
+  <si>
+    <t>Bouwkamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaul </t>
+  </si>
+  <si>
+    <t>Hochstein</t>
+  </si>
+  <si>
+    <t>Anosha</t>
+  </si>
+  <si>
+    <t>Altaf</t>
+  </si>
+  <si>
+    <t>Bobak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanieh </t>
+  </si>
+  <si>
+    <t>Sayadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuichiro </t>
+  </si>
+  <si>
+    <t>Taya</t>
+  </si>
+  <si>
+    <t>McGill University, Montreal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ofir </t>
+  </si>
+  <si>
+    <t>Korch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamutal </t>
+  </si>
+  <si>
+    <t>Slovin</t>
+  </si>
+  <si>
+    <t>Bar-Ilan University, Ramat Gan</t>
+  </si>
+  <si>
+    <t>(ISR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floris </t>
+  </si>
+  <si>
+    <t>Donders Institute for Brain, Cognition and Behaviour, Radboud University, Nijmegen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eelke </t>
+  </si>
+  <si>
+    <t>Spaak</t>
+  </si>
+  <si>
+    <t>Khayat</t>
+  </si>
+  <si>
+    <t>Noam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marina </t>
+  </si>
+  <si>
+    <t>Pavlovskaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haya </t>
+  </si>
+  <si>
+    <t>Abtan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniella </t>
+  </si>
+  <si>
+    <t>Koyfman</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Merav </t>
+  </si>
+  <si>
+    <t>Ahissar</t>
+  </si>
+  <si>
+    <t>ELSC Center for Brain Sciences &amp; Life Sciences Institute, Hebrew University of Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doug JK </t>
+  </si>
+  <si>
+    <t>University of Leicester, Leicester</t>
+  </si>
+  <si>
+    <t>University of Stirling, Stirling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rad</t>
+  </si>
+  <si>
+    <t>Jamal Amani</t>
+  </si>
+  <si>
+    <t>University of Leeds, Leeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institute for Cognitive and Brain Sciences, Shahid Beheshti University, Tehran, </t>
+  </si>
+  <si>
+    <t>(IRAN)</t>
+  </si>
+  <si>
+    <t>(USA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -10561,6 +10711,22 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="4">
@@ -10595,13 +10761,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10936,7 +11107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AE0D66-000C-BD4A-AED3-2568F01E825A}">
-  <dimension ref="A1:BC609"/>
+  <dimension ref="A1:BC612"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -40255,8 +40426,330 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="609" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A609" s="1"/>
+    <row r="605" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A605">
+        <v>611</v>
+      </c>
+      <c r="B605" t="s">
+        <v>3499</v>
+      </c>
+      <c r="C605" t="s">
+        <v>3500</v>
+      </c>
+      <c r="D605" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E605" s="8" t="s">
+        <v>3514</v>
+      </c>
+      <c r="F605" t="s">
+        <v>3515</v>
+      </c>
+      <c r="G605" t="s">
+        <v>2635</v>
+      </c>
+      <c r="AL605" t="s">
+        <v>3516</v>
+      </c>
+      <c r="AM605" t="s">
+        <v>3455</v>
+      </c>
+      <c r="AN605" t="s">
+        <v>3350</v>
+      </c>
+      <c r="AO605" t="s">
+        <v>3471</v>
+      </c>
+    </row>
+    <row r="606" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A606">
+        <v>612</v>
+      </c>
+      <c r="B606" t="s">
+        <v>3501</v>
+      </c>
+      <c r="C606" t="s">
+        <v>3502</v>
+      </c>
+      <c r="D606" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E606" s="8" t="s">
+        <v>3517</v>
+      </c>
+      <c r="F606" t="s">
+        <v>3518</v>
+      </c>
+      <c r="G606" t="s">
+        <v>2631</v>
+      </c>
+      <c r="H606" t="s">
+        <v>3519</v>
+      </c>
+      <c r="I606" t="s">
+        <v>3520</v>
+      </c>
+      <c r="J606" t="s">
+        <v>2631</v>
+      </c>
+      <c r="AL606" t="s">
+        <v>3521</v>
+      </c>
+      <c r="AM606" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="607" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A607">
+        <v>613</v>
+      </c>
+      <c r="B607" s="6" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C607" t="s">
+        <v>3504</v>
+      </c>
+      <c r="D607" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E607" t="s">
+        <v>3505</v>
+      </c>
+      <c r="F607" t="s">
+        <v>3506</v>
+      </c>
+      <c r="G607" t="s">
+        <v>2635</v>
+      </c>
+      <c r="H607" s="6" t="s">
+        <v>3523</v>
+      </c>
+      <c r="I607" t="s">
+        <v>2566</v>
+      </c>
+      <c r="J607" t="s">
+        <v>2635</v>
+      </c>
+      <c r="AL607" t="s">
+        <v>3442</v>
+      </c>
+      <c r="AM607" t="s">
+        <v>3464</v>
+      </c>
+      <c r="AN607" t="s">
+        <v>3524</v>
+      </c>
+      <c r="AO607" t="s">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="608" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A608">
+        <v>614</v>
+      </c>
+      <c r="B608" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C608" t="s">
+        <v>3506</v>
+      </c>
+      <c r="D608" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E608" t="s">
+        <v>3525</v>
+      </c>
+      <c r="F608" t="s">
+        <v>3526</v>
+      </c>
+      <c r="G608" t="s">
+        <v>2631</v>
+      </c>
+      <c r="H608" t="s">
+        <v>3523</v>
+      </c>
+      <c r="I608" t="s">
+        <v>2566</v>
+      </c>
+      <c r="J608" t="s">
+        <v>2631</v>
+      </c>
+      <c r="AL608" t="s">
+        <v>3524</v>
+      </c>
+      <c r="AM608" t="s">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="609" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A609" s="1">
+        <v>615</v>
+      </c>
+      <c r="B609" s="7" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C609" t="s">
+        <v>3508</v>
+      </c>
+      <c r="D609" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E609" s="7" t="s">
+        <v>3528</v>
+      </c>
+      <c r="F609" t="s">
+        <v>3527</v>
+      </c>
+      <c r="G609" t="s">
+        <v>2631</v>
+      </c>
+      <c r="H609" t="s">
+        <v>3529</v>
+      </c>
+      <c r="I609" t="s">
+        <v>3530</v>
+      </c>
+      <c r="J609" t="s">
+        <v>2631</v>
+      </c>
+      <c r="K609" t="s">
+        <v>3531</v>
+      </c>
+      <c r="L609" t="s">
+        <v>3532</v>
+      </c>
+      <c r="N609" t="s">
+        <v>3533</v>
+      </c>
+      <c r="O609" t="s">
+        <v>3534</v>
+      </c>
+      <c r="Q609" t="s">
+        <v>3535</v>
+      </c>
+      <c r="R609" t="s">
+        <v>3536</v>
+      </c>
+      <c r="AL609" t="s">
+        <v>3537</v>
+      </c>
+      <c r="AM609" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="610" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A610">
+        <v>616</v>
+      </c>
+      <c r="B610" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C610" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D610" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E610" t="s">
+        <v>3538</v>
+      </c>
+      <c r="F610" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G610" t="s">
+        <v>2631</v>
+      </c>
+      <c r="AL610" t="s">
+        <v>3539</v>
+      </c>
+      <c r="AM610" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="611" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A611">
+        <v>617</v>
+      </c>
+      <c r="B611" t="s">
+        <v>493</v>
+      </c>
+      <c r="C611" t="s">
+        <v>3511</v>
+      </c>
+      <c r="D611" t="s">
+        <v>2631</v>
+      </c>
+      <c r="AL611" t="s">
+        <v>3540</v>
+      </c>
+      <c r="AM611" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="612" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A612">
+        <v>618</v>
+      </c>
+      <c r="B612" t="s">
+        <v>3512</v>
+      </c>
+      <c r="C612" t="s">
+        <v>3513</v>
+      </c>
+      <c r="D612" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E612" t="s">
+        <v>3541</v>
+      </c>
+      <c r="F612" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G612" t="s">
+        <v>2635</v>
+      </c>
+      <c r="H612" t="s">
+        <v>3542</v>
+      </c>
+      <c r="I612" t="s">
+        <v>935</v>
+      </c>
+      <c r="J612" t="s">
+        <v>2651</v>
+      </c>
+      <c r="K612" t="s">
+        <v>3544</v>
+      </c>
+      <c r="L612" t="s">
+        <v>3543</v>
+      </c>
+      <c r="M612" t="s">
+        <v>2655</v>
+      </c>
+      <c r="AL612" t="s">
+        <v>3546</v>
+      </c>
+      <c r="AM612" t="s">
+        <v>3547</v>
+      </c>
+      <c r="AN612" t="s">
+        <v>3428</v>
+      </c>
+      <c r="AO612" t="s">
+        <v>3548</v>
+      </c>
+      <c r="AP612" t="s">
+        <v>2822</v>
+      </c>
+      <c r="AQ612" t="s">
+        <v>3492</v>
+      </c>
+      <c r="AR612" t="s">
+        <v>3545</v>
+      </c>
+      <c r="AS612" t="s">
+        <v>3492</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Final_Main_Affiliates.xlsx
+++ b/Final_Main_Affiliates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mtoscani@bournemouth.ac.uk/Dropbox/ecvp_2026_website_final_clone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC597FE-B323-634B-ACB6-2389CB18F33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32740709-2EE7-0B42-B652-68ACC608572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17400" xr2:uid="{706473AC-54EE-B349-A1DD-9D10B08BDBB9}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{706473AC-54EE-B349-A1DD-9D10B08BDBB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="56" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>60</v>
+        <v>588</v>
       </c>
       <c r="B56" t="s">
         <v>98</v>
@@ -36075,7 +36075,7 @@
     </row>
     <row r="506" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A506" s="2">
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="B506" t="s">
         <v>913</v>
@@ -39434,7 +39434,7 @@
     </row>
     <row r="582" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A582" s="2">
-        <v>588</v>
+        <v>60</v>
       </c>
       <c r="B582" t="s">
         <v>204</v>

--- a/Final_Main_Affiliates.xlsx
+++ b/Final_Main_Affiliates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mtoscani@bournemouth.ac.uk/Dropbox/ecvp_2026_website_final_clone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933CC981-4535-DF4C-9866-B567FEC0BA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D5FD1B-7F7F-3542-A077-FA1DA4F8EDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{706473AC-54EE-B349-A1DD-9D10B08BDBB9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8845" uniqueCount="3549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8852" uniqueCount="3551">
   <si>
     <t>Submission Id</t>
   </si>
@@ -10684,7 +10684,13 @@
     <t>(USA)</t>
   </si>
   <si>
-    <t>11th_auth_code</t>
+    <t>11th_auth_codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakub </t>
+  </si>
+  <si>
+    <t>Cacek</t>
   </si>
 </sst>
 </file>
@@ -23854,6 +23860,15 @@
       <c r="D258" t="s">
         <v>2630</v>
       </c>
+      <c r="E258" t="s">
+        <v>3549</v>
+      </c>
+      <c r="F258" t="s">
+        <v>3550</v>
+      </c>
+      <c r="G258" t="s">
+        <v>2630</v>
+      </c>
       <c r="AL258" t="s">
         <v>3079</v>
       </c>
@@ -29413,6 +29428,9 @@
       <c r="AG366" t="s">
         <v>687</v>
       </c>
+      <c r="AH366" t="s">
+        <v>2630</v>
+      </c>
       <c r="AL366" t="s">
         <v>3220</v>
       </c>
@@ -40618,17 +40636,26 @@
       <c r="L609" t="s">
         <v>3531</v>
       </c>
+      <c r="M609" t="s">
+        <v>2630</v>
+      </c>
       <c r="N609" t="s">
         <v>3532</v>
       </c>
       <c r="O609" t="s">
         <v>3533</v>
       </c>
+      <c r="P609" t="s">
+        <v>2630</v>
+      </c>
       <c r="Q609" t="s">
         <v>3534</v>
       </c>
       <c r="R609" t="s">
         <v>3535</v>
+      </c>
+      <c r="S609" t="s">
+        <v>2630</v>
       </c>
       <c r="AL609" t="s">
         <v>3536</v>
